--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -5711,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5741,6 +5741,19 @@
         <v>39</v>
       </c>
       <c r="C2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:23:33 UTC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>39</v>
       </c>
     </row>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -5711,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5754,6 +5754,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:39:03 UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>39</v>
       </c>
     </row>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -5711,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5767,6 +5767,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:00:27 UTC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
         <v>39</v>
       </c>
     </row>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -5711,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5780,6 +5780,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:52 UTC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
         <v>39</v>
       </c>
     </row>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -5711,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5793,6 +5793,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:51:32 UTC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>39</v>
       </c>
     </row>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -5711,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5806,6 +5806,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:07:15 UTC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
         <v>39</v>
       </c>
     </row>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5699,6 +5699,1277 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>55805</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Director Center for Laboratory Diagnostics and Systems(Africa CDC)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>African Union</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>in laboratory management. Eight (8) of which should have been served at managerial level and five (5) years at supervisory level.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>$ 78,138</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/director-center-for-laboratory-diagnostics-and-systemsafrica-cdc/</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>AU Values
+AU Values  
+• Respect for Diversity and Team Work             • Think Africa Above all
+• Transparency and Accountability                    • Integrity and Impartiality
+• Efficiency and Professionalism                       • Information and Knowledge Sharing
+Organization Information
+Reports to: Deputy Director General
+Directorate/Department/Organ: Africa CDC
+Division: Office of the Deputy Director General
+Number of Direct Reports:
+Number of Indirect Reports:
+Job Grade: D1
+Number of positions: 1
+Contract Type: Regular
+Location: Addis Ababa, Ethiopia
+Purpose of Job
+The Director Center for Laboratory Diagnostics and Systems is responsible for providing strategic leadership and oversight for the enhancement of laboratory systems and networks across Africa, focusing on improving infrastructure, introducing advanced technologies, and strengthening laboratory capacity in response to diseases of public health importance.
+Main Functions
+Provide strategic direction to Africa CDC/AU on continental efforts to strengthen laboratory systems and networks.
+Lead the development and implementation of initiatives to improve laboratory infrastructure and technologies.
+Oversee and coordinate the development of national laboratory strategic plans and policies, addressing dangerous pathogens.
+Promote comprehensive laboratory quality management systems, including laboratory accreditation.
+Develop, implement, and evaluate programs and projects aimed at enhancing laboratory capacities.
+Lead efforts to improve systems, standards, biosafety, and networks linked to disease surveillance and clinical care.
+Guide research and laboratory investigations for new or improved diagnostic and preventive tools and technologies.
+Develop the capacity of RISLNET for modern advanced molecular technologies and surveillance networks.
+Manage strain banks as repositories for diagnostic and vaccine development against emerging and re-emerging pathogens.
+Establish partnerships with public and private sector organizations, including professional associations, universities, and research organizations.
+Represent Africa CDC at relevant meetings, conferences, and committees in the field of laboratory science.
+Specific Responsibilities
+Oversee, mentor, and guide the development of peer-reviewed research publications in laboratory science.
+Promote and support innovative laboratory practices to enhance patient care, treatment, and strengthen disease surveillance.
+Directly prepare manuscripts for peer-reviewed publication in scientific journals.
+Oversee the translation of program needs into research projects and new research findings into programmatic changes.
+Coordinate the delivery of laboratory services in support of Africa CDC Emergency Response activities as assigned.
+Maintain communication with key stakeholders in laboratory science, fostering a collaborative approach to public health challenges.
+Advocate for the advancement of laboratory diagnostics and systems within the continental public health framework.
+Academic Requirements and Relevant Experience
+Advanced degree (Ph.D., MD, or equivalent) on Clinical Laboratory Science, Pathology, Molecular Biology
+Master degree in Laboratory Sciences, Public Health or Epidemiology.
+With a minimum of 15 years of experience in laboratory management. Eight (8) of which should have been served at managerial level and five (5) years at supervisory level.
+Proven track record in leadership roles within public health or scientific research organizations.
+Experience in international organizations is preferred.
+Demonstrated experience in strategic planning, program implementation, and research in a laboratory or public health setting.
+Essential
+Significant experience of developing senior-level external relationships and securing the highest-level advocacy, including developing and harnessing strong networks across multiple stakeholder groups.
+Advance understanding of stakeholder engagement.
+Extensive experience of leading, motivating and managing teams with the ability to promote a culture of high performance, continuous improvement and innovation.
+Experience and successful track record working in a diverse complex fast paced environments and the ability to influence positive change.
+Academic and Experience Requirements
+Strong leadership and strategic management skills.
+Excellent communication and stakeholder engagement abilities.
+Proficient in risk management and organizational resilience.
+Demonstrated capability in resource mobilization and financial management.
+Ability to work effectively in a diverse, multi-cultural environment.
+Desirable
+Experience of working in international affairs in an international organization
+Experience of working with external partners, funders, and media.
+An understanding of changing economic, political, and social environments affecting the Africa CDC.
+An understanding and analysis of Africa and global political space and atmosphere
+High level of diplomatic and communication etiquette.
+High level interpersonal skills.
+Required Skills
+Result Oriented:
+Strategic thinker, capable of working at a senior level and contributing at Board / Council level
+Entrepreneurial with the ability to input on strategic planning from a commercial standpoint
+Ability to anticipate future opportunities and problems, taking strategic and pre-emptive action
+Ability to set and achieve comprehensive goals for performance and growth
+Passion for working in the developing world and creating positive change
+Leadership:
+Inspire confidence and promote shared values that underpin the ethos of the African Union and Africa CDC
+Inspires others, is visible, adaptive, authentic and engenders trust
+Visible leadership, promoting collective leadership for taking teams through significant programmes of change.
+Passion and commitment for continuous improvement
+Ambitious individual who has personal drive to succeed and develop their own career, and support their teams to strive for excellence.
+Political and diplomatic prowess
+Building and Managing Teams:
+Directs and coaches’ others throughout the organisation and enables people to perform at their best.
+Ability to recognise and cultivate rising talent.
+Creates a positive team environment.
+Creates cohesion, developing synergies and achieves through common goals.
+Communication and Interpersonal Skills:
+High emotional and social intelligence.
+Collaborative, supportive, calm under pressure, solution focused and able to lead others effectively in such a way that encourages maximum performance and engagement.
+Required Skills
+Exceptional communicator both in writing and in person to a range of audiences.
+Relationship Management:
+Exceptional relationship-building and interpersonal skills with the ability to influence and negotiate with a wide range of stakeholders and partners.
+The gravitas and credibility to influence both within and beyond the organisation
+Analytical Skills:
+Conceptual thinker, innovative and capable of complex problem solving
+The ability to work well under pressure and take a considered, measured position
+Results Orientated:
+Desire for success and the motivation to constantly seek improvement
+Ability and drive to manage organisational complexity
+A high level of resilience with the ability to initiate and drive decisions
+Tenacious, adaptable and the ability to get things done
+The highest levels of self-awareness, commitment, and integrity
+A proven commitment to fairness, inclusion, equality, diversity, and transparency
+Values: A strong commitment to the African Union and Africa CDC values
+Notes
+The requirements and responsibilities contained in this job description do not create a contract of employment and are not meant to be all-inclusive. It may be changed by the role manager during employment on an as-needed basis.
+Footer
+TENURE OF APPOINTMENT:
+The appointment will be made on a regular term contract for a period of three (3) years, of which the first twelve months shall be considered as a probationary period. Thereafter, the contract will be for a period of two years renewable, subject to satisfactory performance and deliverables.
+GENDER MAINSTREAMING:
+The African Union is an equal opportunity employer and qualified women are strongly encouraged to apply.
+LANGUAGES:
+Proficiency in one of the AU working languages (Arabic, English, French, Kiswahili, Portuguese, and Spanish) and fluency in another AU language is an added advantage
+REMUNERATION:
+Indicative basic salary of US$ 78,138.00 (D1 Step1) per annum plus other related entitlements e.g. Post adjustment (46% of basic salary), Housing allowance US$ 26,208.00 (per annum), and education allowance (100% of tuition and other education-related expenses for every eligible dependent up to a maximum of US$ 10,000.00 per child per annum), for internationally recruited staff and a maximum of $3,300 per child per annum for locally recruited staff.
+How To Apply
+Applications must be submitted no later than 26 October, 2026 11h59 p.m. EAT.
+-Only candidates who meet all job requirements and are selected for interviews will be contacted. -Consideration will be given only to those candidates who have submitted a fully completed online application with a curriculum vitae (CV),
+https://jobs.au.int/job/Director-Center-for-Laboratory-Diagnostics-and-Systems%28Africa-CDC%29/3098-en_US\
+an African passport, and the required academic qualifications, such as Diplomas, Bachelor’s degrees, Master’s degrees and any relevant certificate in line with the area of expertise. -The African Union is an equal opportunity employer, and female candidates are strongly encouraged to apply.
+-Candidates from less represented countries within the African Union are strongly encouraged to apply for positions that fit their profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>55804</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Director General</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>African Union</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Master’s degree in Public Administration, Business Administration, Finance, Economics, Law, Management, International Relations or a related field from a recognized institution plus fifteen (15) years of relevant professional experience with at least ten (10) years served in a senior management role preferably in an inter-governmental organization or national government/public service, international or regional institution, and a minimum of five (5) years of direct supervisory experience.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>$ 100,017</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/director-general/</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>AU Values
+• Respect for Diversity and Team Work            • Think Africa Above all
+• Transparency and Accountability                   • Integrity and Impartiality
+• Efficiency and Professionalism                      • Information and Knowledge Sharing
+Organization Information
+Reports to: Chairperson of the African Union Commission
+Directorate/Department/Organ: Bureau of the Chairperson
+Number of Direct Reports: 3
+Number of Indirect Reports: 2
+Job Grade: D2
+Number of Positions: 1
+Contract Type: Regular 
+Location: Addis Ababa, Ethiopia
+Purpose of Job
+To assist the Chairperson in the exercise of his/her responsibility for the overall coordination and effective functioning of the Commission, including by supporting, under the authority and guidance of the Chairperson and in full consultation with the Deputy Chairperson and the Commissioners, the operational coordination of the Commission’s Departments and non-elected staff, with a view to ensuring high performance, results and impact.
+Main Functions
+Supports the Chairperson in the identification and operationalization of the Commission’s priorities.
+Under the guidance of the Chairperson and in consultation with the senior leadership, supports the translation of the Commission’s priorities into annual targets and goals and the establishment of a Commission-wide framework for monitoring and tracking progress.
+Provides regular reports to the Chairperson of the Commission on portfolio and service delivery.
+Regularly consults and provide briefing  to the Deputy Chairperson of the Commission on service delivery.
+Works closely with the Cabinet of the Chairperson to ensure that the Chairperson’s strategic directions and priorities are effectively reflected in the delivery of the strategic priorities of the Commission.
+Supports the leadership in the implementation of the AU Institutional Reform Agenda and other reform initiatives across the Commission.
+Monitors and tracks progress in the delivery of the Commission’s annual performance targets.
+Consults with and supports other members of the senior leadership team, under the guidance of the Chairperson, to promote strategic coherence and synergy in the implementation of the Commission’s programme and the delivery of high-impact results for the continent.
+Cultivates a knowledge management culture through the promotion of research and publications to ensure knowledge sharing and transfer across the Commission, in coordination with the relevant departments; and
+Carries out his/her Commission-wide coordination and performance monitoring functions under the authority, guidance and direction of the Chairperson.
+Specific Responsibilities
+Assists the Chairperson and the Commission in the preparation of the annual report of the Commission to the policy organs.
+Coordinates, under the guidance of the Chairperson and in close consultation with the senior leadership, including the Deputy Chairperson and Commissioners, the preparation of the Commission’s annual performance targets for approval through the appropriate processes.
+Convenes, as authorized by the Chairperson, meetings of Portfolio Directors to monitor and track progress in the delivery of the Commission’s annual work plan performance targets.
+Convenes Service Directors’ meetings, in consultation with the Cabinet of the Chairperson, and the Cabinet of the Deputy Chairperson, each concerning their respective departments, to monitor and track progress in the delivery of the Commission’s annual work plan performance targets.
+Reports to the Chairperson on progress and challenges in the implementation of the annual work plan.
+Performs any other duties assigned by the Chairperson.
+Academic Requirements and Relevant Experience
+Master’s degree in Public Administration, Business Administration, Finance, Economics, Law, Management, International Relations or a related field from a recognized institution plus fifteen (15) years of relevant professional experience with at least ten (10) years served in a senior management role preferably in an inter-governmental organization or national government/public service, international or regional institution, and a minimum of five (5) years of direct supervisory experience.
+The age limit for entry into career service shall not be more than fifty-five (55) years of age.
+Required Skills
+Ability to lead and manage complex organizations at the national, regional or international level.
+Proven track record in coordination, consultation and consensus-building across portfolios and in complex institutional environments.
+Ability to set clear standards for accountability, probity, value for money and risk management.
+Ability to propose new ideas to the leadership on improving work across silos in a complementary and synergistic way for a prosperous and peaceful Africa.
+Proven track record of change management and accomplishments at the regional, national or international level with strong resource mobilization, political and diplomatic skills.
+Demonstrated ability to successfully lead a multicultural team and establish harmonious and effective working relationships both within and outside the organization.
+Interpersonal and negotiation skills.
+Planning and organizing skills.
+Knowledge and working understanding of the African Union.
+Communication, presentation and report-writing skills.
+Proficiency in one of the AU official working languages (French, English, Portuguese, Arabic, Swahili, Spanish) and fluency in another AU language(s) is an added advantage.
+Leadership Competencies
+Strategic Focus
+Developing Organisational Capability
+Change Leadership
+Strategic Risk Management
+Core Competencies
+Building Partnerships
+Drives Accountability Culture
+Learning Orientation
+Communicating with impact
+Functional Competencies
+Conceptual Thinking
+Job Knowledge and information sharing
+Drive for Results
+Fosters Innovation
+TENURE OF APPOINTMENT:
+The appointment will be made on a regular term contract for a period of three (3) years, of which the first twelve months shall be considered as a probationary period. Thereafter, the contract will be for a period of three years renewable, subject to satisfactory performance and deliverables.
+GENDER MAINSTREAMING:
+The AU Commission is an equal opportunity employer and qualified women are strongly encouraged to apply.
+LANGUAGES:
+Proficiency in one of the AU working languages (Arabic, English, French, Kiswahili, Portuguese, and Spanish) is mandatory and fluency in another AU language is an added advantage
+REMUNERATION:
+Indicative basic salary of US$ 100,017.00 (D2 Step 1) per annum plus other related entitlements e.g. Post adjustment (46% of basic salary), Housing allowance US$ 26,208.00 (per annum), and education allowance (100% of tuition and other education-related expenses for every eligible dependent up to a maximum of US$ 10,000.00 per child per annum), for internationally recruited staff and a maximum of $3,300 per child per annum for locally recruited staff.
+How To Apply
+Applications must be submitted no later than October 26, 2026 11h59 p.m. EAT.
+-Only candidates who meet all job requirements and are selected for interviews will be contacted.
+https://jobs.au.int/job/Director-General/3103-en_US
+-Consideration will be given only to those candidates who have submitted a fully completed online application with a curriculum vitae (CV),</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>55803</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Finance Director (Africa CDC)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>African Union</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Accounting / Finance, NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Master’s degree in Accounting, Finance, Business Management with at least fifteen (15) years of experience, out of which eight (8) years should be at a managerial level, and five (5) in a direct supervisory role.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>$ 78,138</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/finance-director-africa-cdc-2/</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>AU Values
+• Respect for Diversity and Team Work            • Think Africa Above all
+• Transparency and Accountability                  • Integrity and Impartiality
+• Efficiency and Professionalism                     • Information and Knowledge Sharing
+Download CV Template Here
+Please download the African Union CV template here. Kindly fill it out correctly and upload it to the “Resume” tab of your profile. This is MANDATORY.
+Organization Information
+Reports to: Director General
+Directorate/Department/Organ: Africa CDC
+Division: Office of the Director General
+Number of Direct Reports:   4
+Number of Indirect Reports: 10
+Job Grade: D1
+Number of Position: 1
+Contract of Position: Regular
+Location: Addis Ababa, Ethiopia
+Purpose of Job
+The Director of Finance will provide strategic direction and leadership in managing the operations of the Finance Directorate in order to achieve the Africa CDC strategic objectives and goals. S/he will work with Africa CDC executive team to build and deliver financial policies and strategies that improve the organization’s financial status. S/he will oversee all the financial operations within each Division/Unit to ensure they’re spending within the budget and following the financial policies laid out by the AUC.
+The Director of Finance will also analyze the financial performance of Africa CDC and build reports for the executive team to review and provide feedback. S/he will also research and review Africa CDC’s financial statistics to make forecasts and projections that help to build more comprehensive budgets. S/he will develop strategies to assess, manage and minimize any potential financial risks.
+Africa CDC invites applications from qualified individuals who are citizens of AU Member States to apply for the position of Director of Finance.
+Main Functions
+The main duties will include, but not limited to establishing targets, developing budgets, and performing financial analysis. The ultimate goal is to guide Africa CDC towards success.
+Develops and executes the overall strategy for the directorate and ensures alignment with overall organizational strategy
+Manages and supervises employees within the directorate, ensures the timely delivery of the directorate’s goals and effective staff performance evaluation
+Drives the implementation and monitoring of policies, strategies and programs to contribute to the effective implementation of relevant AU Policy Organs Decisions
+Ensures the delivery of the directorate’s annual targets in line with the organization’s overall goals and maintains robust departmental monitoring and evaluation systems.
+Provides strategic financial leadership for the operationalization and oversight of the African Epidemic Fund, ensuring governance, disbursement mechanisms; as well as all other Special Accounts and Trust Funds held by Africa CDC
+Designs and oversees innovative financing solutions including blended finance instruments, catalytic capital structures and risk-sharing mechanisms, aligned with Africa CDC’s strategic framework.
+Provides technical leadership and ensures efficient functioning of all Divisions within the directorate
+Manages the work of the Directorate and supervises direct reports to ensure their effective performance in line with the organization’s performance management policy and system.
+Leads the directorate and ensures effective management of personnel, budget, performance, program quality, employee relations matters and training in conformity with relevant rules, policies and procedures.
+Builds and maintains good working relations and collaboration with other directorates/departments.
+Develops and maintains regular working relations with senior stakeholders in Member State and partner institutions.
+Coordinates meetings between the organization and relevant partners
+Ensures the preparation of periodic financial and budget execution reports and other reports
+Ensures the effective management of funds contributed to the organization
+Implements and maintains thematic partnerships in support of the mandate of the Directorate
+Develops and oversees policy development and guidelines in line with the organization’s legal framework
+Designs policies consistent with Africa CDC’s strategic goals and mandate in order to address the pertinent issues in the relevant area
+Prepares and oversees integrated programs, projects and overall activities of the organization.
+Maintains a positive work environment that facilitates collaboration and information sharing and is conducive to attracting, retaining, and motivating diverse talent.
+Develops and maintains standard operating procedures (SOP’s) for the Directorate
+Manages risks, develops mitigation measures and ensures business continuity of the directorate.
+Specific Responsibilities
+Oversee the financial strategic planning of the institution by evaluating its performance and potential risks.
+Develops and implements effective, responsive and efficient financial and budgetary strategies, policies and management systems, as per the international accounting standards.
+Perform regular financial analysis and the annual financial statements for Africa CDC
+Develop budgets that meet the requirements of institution departments
+Establish targets and manage all accounting and finance employees including management accountants and internal auditors.
+Supervise all audit and internal control processes.Prepare detailed reports on the institution’s financial performance.
+Guarantee compliance with financial laws and guidelines.
+Recognize patterns in institution spending, revenue, and recommend solutions to any problem areas.
+Coordinate with external financial entities on behalf of the institution.
+Contributes to the planning and development of Financial Accounting policies and policy to execute budgetary programs, Rules, Regulations and Procedures and ensures their implementation within Africa CDC.Collects and manages statutory and other funds owed to Africa CDC.
+Ensures inter-departmental coordination in programming and the budgetary process.
+Assesses     the    efficiency    and    effectiveness    of    programs    in realizing organizational goals and objectives.
+Promotes sound financial management by ensuring adherence and compliance with International Public Sector accounting standards (IPSAS), the AU Financial Rules and Regulations, Policies, Systems and Procedures.
+Leads the financial operationalization and oversight of the African Epidemic Fund, ensuring governance, disbursement mechanisms; as well as all other Special Accounts and Trust Funds held by Africa CDC
+Supports the designs and operationalization of innovative financing solutions held by Afria CDC including blended finance instruments, catalytic capital and risk-sharing mechanisms
+Seeks continuous improvement and cost effectiveness in the delivery of services.
+Responsible and accountable for managing the human resources component of the Directorate of Finance.
+Provides accurate, reliable and timely accounts of Africa CDC and provision of value adding professional and strategic advice to Member States and internal customers.
+Prepares and issues instructions relating to budget preparation.
+Oversees the preparation of the programme budget of Africa CDC and follows up its implementation.
+Organizes coordination meetings on programming and budgeting.
+Proposes training programmes relating to programme designing, programme coordination, and budget preparation.
+Manages the Programme Budget of the institution;
+Initiates, proposes, manages and implements financial policies.
+Promotes awareness of best practices in financial management and internal financial control systems.
+Controls budget execution and processes payments
+Invests excess liquidity as authorized
+Facilitates the conduct of an external audit.
+Ensures effective implementation of Financial Rules and Regulations
+Ensures safe custody of all liquid Assets of Africa CDC
+Ensures prompt recovery of all receivables owed to the Africa CDC
+Produces periodic financial and budget execution reports, annual financial statements, and other specific mission reports, in accordance with Financial Rules and Regulations
+Advises the Director General on policy and strategy matters and ensures alignment of Africa CDC’s application of financial policy, programming guidelines, accounting system, budgeting guidelines, and asset safeguard systems with those of the African Union
+Provides technical guidance and ensures efficient functioning of supervised Divisions
+Builds and maintains good working relations with other Departments/Directorates/Offices within Africa CDC and beyond the African Union level
+Develops and maintains regular working relations with appropriate agencies of Member States and partners and ensures the timely collection of contributions from Member States
+Performs any other relevant duties as may be assigned by the supervisor.
+Academic Requirements and Relevant Experience
+Master’s degree in Accounting, Finance, Business Management with at least fifteen (15) years of experience, out of which eight (8) years should be at a managerial level, and five (5) in a direct supervisory role.
+Additional education and experience in public health administration, or related programme management and operations area will be an added advantage.
+Membership in an internationally recognized professional accounting body (CA, CPA, ACCA, CIMA, Expert Comptable) is mandatory.
+Relevant specialist professional qualifications are an added advantage.
+Experience in leading financial operations, planning, and analysis for various organizations.
+Proven experience in managing budgets, forecasts, audits, compliance, and risk management activities.
+Experience in implementing strategic initiatives to improve financial performance, optimize resources, and enhance stakeholder value. Experience in providing technical support.
+Required Skills
+Required skills and competencies: 
+In-depth knowledge of accounting software, corporate principles, and financial analysis
+Excellent communication, interpersonal, and outstanding leadership abilities
+An analytical mind with good organizational skills
+Knowledge of International Public Sector Accounting Standards (IPSAS)
+Ability to develop multi-annual plans and budgets based on Result-Based Management
+Communication and reporting skills with internal and external stakeholders
+Computer literacy – knowledge of major accounting systems, especially SAP-ERP, shall be an advantage
+Ability to organize and motivate others and to work in a multi-cultural environment
+Strong skills in financial reporting, data analysis, accounting, and business intelligence tools
+Confident in his/her ability to bring expertise and leadership to the organization and contribute to its growth and success.
+Excellent drafting and reporting skills
+Ability to mentor teams on the same
+Planning and organizational skills
+Proficiency in one of the AU working languages (Arabic, English, French, Portuguese, Kiswahili, and Spanish) and fluency in another AU language is an added advantage
+Have a commitment to the Africa CDC.
+Leadership Competencies
+Strategic Focus
+Developing Organisational Capability
+Change Leadership
+.Strategic Risk Management
+Core Competencies
+Building Partnerships
+Drives Accountability Culture
+Learning Orientation.
+Communicating with impact
+Functional Competencies
+Conceptual Thinking
+Job Knowledge Sharing
+Drive for Result ….
+Fosters Innovation
+Footer
+TENURE OF APPOINTMENT:
+The appointment will be made on a regular term contract for a period of three (3) years, of which the first twelve months shall be considered as a probationary period. Thereafter, the contract will be for a period of two years renewable, subject to satisfactory performance and deliverables.
+GENDER MAINSTREAMING:
+The African Union is an equal opportunity employer and qualified women are strongly encouraged to apply.
+LANGUAGES:
+Proficiency in one of the AU working languages (Arabic, English, French, Kiswahili, Portuguese, and Spanish) is mandatory and fluency in another AU language is an added advantage
+REMUNERATION:
+Indicative basic salary of US$ 78,138.00 (D1 Step1) per annum plus other related entitlements e.g. Post adjustment (46% of basic salary), Housing allowance US$ 26,208.00 (per annum), and education allowance (100% of tuition and other education-related expenses for every eligible dependent up to a maximum of US$ 10,000.00 per child per annum), for internationally recruited staff and a maximum of $3,300 per child per annum for locally recruited staff.
+How To Apply
+Applications must be submitted no later than October 20, 2026, 11:59 p.m. EAT.
+-Only candidates who meet all job requirements and are selected for interviews will be contacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>55802</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ICLA Technical Assistant</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Norwegian Refugee Council</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Familiarity with Ethiopian commercial law, labor law, and regulatory frameworks</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>id="how-to-apply-section" class="job-detail-description"&gt;
+How To Apply
+Apply here!
+https://ekum.fa.em2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_2019/jobs/preview/21800/?location=Ethiopia&amp;locationId=300000000306687&amp;locationLevel=country&amp;mode=location
+Female Candidates are highly encouraged to apply!</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/icla-technical-assistant/</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>About the Job
+Generic Role and responsibilities:
+Develop annual activity and work plans
+Promote and share ideas for improvement and necessary changes in activities
+Cooperate with relevant partners and local authorities
+Implement delegated ICLA programme activities according to plan of action
+Ensure proper filing of all project documents
+Prepare and develop progress reports as required by management
+Ensure that projects target project participants most in need, and explore and asses new and better ways to assist
+Demonstrate commitment to NRC’s mission, vision and value
+Specific responsibilities
+Provide and Facilitate information, counselling, legal assistance project activities to project participants in line with NRC policies, strategies, and work plans.
+Accurately record all ICLA activities in line with NRC policy and using templates and guidance provided by NRC.
+Facilitate and provide information on legal and civil documentation (LCD), rights and entitlements to project participants in accordance with agreed information scripts.
+Provide legal counselling on LCD and HLP topics
+Assist ICLA Project participants to resolve their LCD and HLP issues independently.
+Assist Provision LCD and HLP training using NRC approved materials and templates.
+Participate in assessments, monitoring and profiling exercises as agreed with line managers.
+Ensure that ICLA activities are carried out in line with appropriate NRC ICLA SOPs.
+Perform any other tasks as requested by ICLA line managers.
+About You
+Generic professional competencies:
+Experience from working in a humanitarian/recovery context
+Documented results related to the position’s responsibilities
+Strong communication, interpersonal, analytical and negotiation skills
+Ability to prioritise responsibilities, carry out multiple tasks simultaneously, and meet deadlines
+Context/ Specific skills, knowledge and experience:
+University Degre Law, Political Science, Sociology, or any related field to this position
+A minimum of 1 year work experience in similar field of work.
+Understanding Humanitarian intervention and contested areas
+Willing to spend more time at the filed level and ready to learn
+Knowledge of humanitarian principles and code of conduct is essential.
+Knowledge of Amharic language is mandatory and good in spoken and written English
+Personal Qualities:
+Diplomatic
+Ability to work under pressure and with limited supervision in a challenging environment
+Pro-active, goal-oriented and results driven
+Flexible and creative
+Excellent communication skills
+A sense of humor
+Behavioral competencies
+Handling insecure environment
+Planning and delivering results.
+Empowering and building trust
+Communicating with impact and respect</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>55801</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Partnerships and Private Sector Engagement Manager</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Norwegian Refugee Council</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>• Development-oriented; • Creativity; • Strong coordination and networking skills; Ability to deliver quality work within deadlines; Ability to coordinate multiple tasks and work under pressure.; ability to build strong working relationships</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>id="how-to-apply-section" class="job-detail-description"&gt;
+How To Apply
+Application procedure
+Qualified and interested candidates who meet the above requirements are invited to submit their application letters, along with an updated curriculum vitae (CV) that includes a daytime telephone number and contact details for three work-related referees. Please attach photocopies of your most relevant educational certificates, testimonials, and work experience documents and copy of National ID.
+All applications must be submitted to NRC using this application link – Click here to apply: https://ekum.fa.em2.oraclecloud.com/hcmUI/CandidateExperience/en/job/21784/share/300001448008781?utm_medium=jobshare&amp;utm_source=Internal%20Job%20Share
+NB: only shortlisted candidates shall be contacted.
+Female candidates are strongly encouraged to apply and on job training will be  provided!
+NRC only advertises job openings in the organization website through Ethiojobs, and any advertisements published on other websites or social media do not represent our organization.</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/partnerships-and-private-sector-engagement-manager/</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>About the Job
+Generic responsibilities
+The following is a brief description of the role.
+Lead the development and implementation of the localisation component of NRC’s country strategy , including the development and institutionalisation of the localisation strategy, guidance , systems and tools, following NRC’s global guidance.
+Lead and coordinate the deployment of the partnership approach across all the offices.
+Ensure all partners and partnerships adhere to NRC policies, handbooks, guidelines and donor requirements.
+Support the overview and maintenance of projects implemented with Partners at the country office level, including providing helpdesk support to partners on compliance with NRC and donor requirements.
+Maintain relations with a range of partners and work with the country and area teams to identify and pursue suitable and aligned potential partners hips .
+Specific responsibilities :
+Partnership strategy development :
+Develop localisation strategy for NRC Ethiopia, tools, guidance notes, training material , and ensure reporting on Partnership’s component is timely and accurate.
+Conduct Due Diligence for each partner and evaluate their capacity for potential strategic partnership with NRC.
+Lead the development, drafting, and execution of the strategy implementation plan, ensuring efficient monitoring and evaluation processes are in place.
+Facilitate coordination across the Country Office and Area Offices to ensure consistent implementation of the partnership strategy, enabling effective collaboration.
+Develop and maintain an up-to-date partner mapping .
+Build a network of key partners and stakeholders, keeping abreast of evolving trends (social, economic, and political), including the application of innovation to partnership and project development .
+Establish and continuously enhance a robust information management system for the management of partnership information , including partners’ profiles, contract management information, due diligence processes, assessments and reporting status, among others
+About You
+Generic professional competencies
+3-5 years of experience in working in a humanitarian/recovery/human rights or development context
+University degree combined with relevant professional background .
+Knowledge of humanitarian principles.
+Experience in managing and implementing programs in humanitarian contexts .
+Ability to work independently and proactively.
+Ability to prioritise work given multiple competing deadlines.
+Fluency in English and Amharic , both written and verbal
+Context-related skills, knowledge and experience
+Solid understanding of the Ethiopian civil society and private sector context.
+Documented/proven results related to the position’s responsibilities, particularly in private sector engagement and partnership relations , management and/or coordination.
+Excellent networking, coordination, training and facilitation skills
+Excellent communication skills, both written and verbal
+Excellent interpersonal skills, proactive , self-motivated and a self-starter.
+Excellent attention to detail, organisational skills and discretion with confidential information
+Previous experience working in complex and volatile contexts is an asset.
+Programme management b ackground is an asset. Experience in NRC thematic areas (e.g. ICLA, Shelter, LFS, Protection, Education etc.) is a strong asset.
+Background in Market Systems Development is a strong asset.
+Behavioural competencies
+Ability to handle an insecure environment
+Respectful and able to work well with people of diverse backgrounds
+Critical thinker with astute analysis skills
+Ability to communicate with impact and respect Adaptable and able to cope with change</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>55800</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Head of Unit – Treasury (Finance)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>African Union</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Accounting / Finance, NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A Master’s Degree in Finance/Accounting or related field with seven (7) years of relevant work experience out of which 3 years should have been served at supervisory level.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>$ 37,453</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/head-of-unit-treasury-finance/</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>AU Values
+• Respect for Diversity and Team Work             • Think Africa Above all
+• Transparency and Accountability                 • Integrity and Impartiality
+• Efficiency and Professionalism                  • Information and Knowledge Sharing
+Organization Information
+Reports to: Head of Finance Management Division
+Directorate/Department: Finance
+Division : Treasury 
+Number of Direct Reports: 2
+Number of Indirect Reports: 1 
+Job Grade: P3
+Number of Positions: 1
+Contract Type: Regular
+Location: Addis Ababa, Ethiopia
+Purpose of Job
+To provide technical support for the effective and transparent expenditure of AU and ensure compliance  to  sound financial management principles.
+Main Functions
+Provides support in the preparation and Implement the programmes developed out of the Division’s strategic plan;
+Ensures effective coordination and implementation at various levels;
+•    Liaises with Member States, Regional Economic Communities (RECs) and other stakeholders including on relevant matters;
+•    Prepares and develops reports, budget and work programmes related to the functioning of the Division;
+•    Provides support to the development of resource mobilization strategy with stakeholder’s coordination;
+•    Manages and supervise employees under his/her supervision with regard to organization and performance evaluation;
+•    Conducts complex analysis and generate accurate reports in a timely manner for the Division and AU’s internal use;
+•    Liaises with the various Departments/Units of the Commission for coordination and alignment purposes;
+•    Prepares budgets for the Division in accordance with relevant frameworks.
+•    Provides support for the promotion of the activities of the Division including preparing leaflets, guidelines and fact sheets as may be required;
+•    Contributes to the development of strategies, policies, programmes and plans.
+Specific Responsibilities
+•    Maintains the register of all assets and ensure routine cash counts are undertaken monthly and quarterly;
+•    Submits at the beginning of each month, a cash-forecast/projection for management use;
+•    Submits daily cash balance reports for effective cash monitoring to ensure there are no overdrafts;
+•    Monitors investment portfolios daily including Working capital, High-Yield, Escrow, and other portfolios to ensure timely actions are takes as the market swings;
+•    Ensures an up-to-date treasury policy that is constantly reviewed and updated annually taking into account market info and other regulatory changes including setting up definition of the risk tolerance;
+•    Reviews controls around treasury systems and ensure they are adequate and are operating all the time and should there be gaps, that compensatory controls are introduced and further system enhancement is recommended;
+•    Manages relationships with financial service providers ensuring that their service charges and other aspects are within terms of agreement;
+•    Ensures payments transfers are executed timely and transfers are made to the bank within two days of file completion and delays are monitored and logged;
+•    Ensures payment platforms are in good working order with all control protocols update and being reviewed periodically;
+•    Ensures the liquidity (day to day management of cash) needs of each of the entities in the organization are met in compliance with the Treasury Policy;
+•    Prepares and submits AU’s cash flow forecasts and undertake financial modelling to determine periods of surpluses and deficits;
+•    Schedules and keeps track of records of quarterly investment meetings and ensure all matters of investments requiring decisions and prior period updates are presented before the committee a few days before the meeting;
+•    Ensures long and short term strategies, policies, systems and other applicable regulatory frameworks are up to date and that requisite information including the risk tracker is maintained in the Cash and liquidity modules of AUC SAP ERP;
+•    Prepares and submits monthly investment and other asset reports accompanied by market/Trend information;
+•    Supervises staff and monitor all payments online and otherwise while ensuring there are no transfer/payment delays and that associated risks are timely identified, mapped, classified and timely mitigated;
+•    Undertakes Overall Treasury system continuous improvement in light of environmental changes and other recommendations;
+•    Ensures vibrant client relationship with all financial institutions (including Banks) AU has dealings with;
+•    Forecasts daily cash requirements and execute daily financing decisions;
+•    Determines the organization’s tax position and the applicability of taxable/non-taxable instruments;
+•    Reviews and recommends changes to the investment policies based on the market conditions;
+•    Prepares AU’s cash flow forecasts and perform financial modelling;
+•    Evaluates, develops and implements cash management systems to optimize efficiencies;
+•    Understands and manages appropriate accounting procedures and processes to meet the organization’s needs;
+•    Determines procurement of funds and monitor investments and collections;
+•    Conducts benchmark studies of banks and their services to evaluate whether it fits AU requirements;
+•    Ensures that project/department milestones/goals are met and adhering to approved budgets;
+Academic Requirements and Relevant Experience
+  A Master’s Degree in Finance/Accounting or related field with seven (7) years of relevant work experience out of which 3 years should have been served at supervisory level.
+Or
+A Bachelor’s degree in Finance/Accounting or related field with ten (10) years of relevant work experience out of which 3 years should have been served at supervisory level.
+Required Skills
+•    Financial Management and Analytical skills;
+•    Interpersonal and negotiation skills
+•    Presentation, report writing and communication skills;
+•    Computer skills with practical knowledge of Microsoft Office Suite.
+•    Planning and organizing skills
+•    Ability to effectively lead, supervise, mentor, develop and evaluate staff
+•    Proficiency in one of the AU working languages, fluency in another AU language is an added advantage
+Leadership Competencies
+Strategic Insight
+Developing Others
+Managing Risk
+Change Management
+Core Competencies
+Building Relationships
+Foster Accountability Culture
+..Learning Orientation
+Communicating with impact
+Functional Competencies
+Conceptual Thinking
+Drive for Results
+Job Knowledge Sharing
+Fosters Innovation
+TENURE OF APPOINTMENT:
+The appointment will be made on a regular term contract for a period of three (3) years, of which the first twelve months shall be considered as a probationary period. Thereafter, the contract will be for a period of three (3) years renewable, subject to satisfactory performance and deliverables.
+GENDER MAINSTREAMING:
+The AU Commission is an equal opportunity employer and qualified women are strongly encouraged to apply.
+LANGUAGES:
+Proficiency in one of the AU working languages (Arabic, English, French, Kiswahili, Portuguese, and Spanish) is mandatory and fluency in another AU language is an added advantage
+REMUNERATION:
+Indicative basic salary of US$ 37,453.00 (P3 Step1) per annum plus other related entitlements e.g. Post adjustment (46% of basic salary), Housing allowance US$ 22,932.00 (per annum), and education allowance (100% of tuition and other education-related expenses for every eligible dependent up to a maximum of US$ 10,000.00 per child per annum), for internationally recruited staff and a maximum of $3,300 per child per annum for locally recruited staff.
+How To Apply
+Applications must be submitted no later than October 30, 2026 at 11h59 p.m. EAT.
+-Only candidates who meet all job requirements and are selected for interviews will be contacted.
+-Consideration will be given only to those candidates who have submitted a fully completed online application</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>55799</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Digital Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Excel Consultrade PLC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Business Administration</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/digital-marketing-specialist/</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Job Summary
+We are looking for an execution-focused Digital Marketing Specialist to support the delivery of digital marketing campaigns for a major brand and marketing project.
+Key Responsibilities
+ Digital Marketing strategy Development and Execution
+● Plan and execute social media and digital campaigns.
+● Develop and Manage content calendars and social media publishing.
+● Set up and optimize Meta Ads, TikTok Ads and other paid campaigns
+● setup, Monitoring and Management Of Lead Generation Funnels(Meta, Telegram Bot)
+● Generate and qualify leads through digital channels.
+● Develop landing-page and lead-generation funnels.
+● Manage community engagement, comments and inboxes.
+● Track campaign KPIs including reach, engagement, CPL, CPA and conversions.
+● Conduct basic SEO audits, keyword research and on-page optimization.
+● Support CRM-based lead tracking and attribution.
+● Prepare weekly/monthly performance reports and recommend improvements.
+● Coordinate with creative and marketing teams.
+Requirements
+ Bachelor’s degree in Marketing, Digital Marketing, Communications, Business or related field.
+● 2–3 years practical digital marketing experience.
+● Hands-on experience with Meta Ads Manager.
+● Knowledge of social media analytics, lead generation and performance marketing.
+● Intermediate SEO knowledge.
+● Strong content planning and copywriting skills.
+● Basic UI/UX understanding.
+● Odoo/CRM knowledge is an advantage.
+● Strong analytical and execution skills.
+● Optional- Occasionally Willing to Get Filmed For social Media content
+Ideal Candidate
+Proactive • Analytical • Creative • Organized • Data-driven • Results-oriented
+This is NOT a social-media posting-only role. The candidate must be able to plan, execute, measure and optimize campaigns.
+Women are strongly encouraged to apply.
+How To Apply
+Application   Send CV + Portfolio.
+Shortlisted candidates will complete a practical digital marketing assessment.
+Email: kali.excel123@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>55798</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Water &amp; Irrigation Expert</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Menschen fuer Menschen Foundation</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Communication; Irrigation Engineering/ Water Resource Engineering; Agriculture Engineering</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>id="how-to-apply-section" class="job-detail-description"&gt;
+How To Apply
+Interested applicants fulfilling the above requirement can send a non-returnable application mentioning the job title and duty station in the subject line, CV, and copies of relevant documents to the following address or in person to the project office stated above within 10 days from the date of announcement.
+Menschen fuer Menschen
+P.O.BOX  2568
+ADDIS ABABA, ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/water-irrigation-expert-2/</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>About the Job
+Menschen fuer Menschen Foundation- is a nongovernmental, nonreligious and nonpartisan humanitarian organization involved in Integrated Rural Development activities wishes to invite applicants with the following qualification and experience for Kawo Koyisha Integrated Rural Development Project:
+ Position:  Water &amp; Irrigation Expert
+No. Required:          1 (One)
+Duty stations:  Kawo Koyisha Integrated Rural Development Project (KKIRDP) (Wolayita Zone, Gesuba Town)
+MAIN DUTIES:
+Identify, study, and design small scale irrigation &amp; water supply schemes.
+Supervise all irrigation activities of the project and water supply.
+Produce design and bill of quantities for irrigation &amp; water supply works.
+Implement and supervise flood protection structures at river banks.
+Produce operational plan of action and organize reports on regular basis.
+Language:                A good command of spoken and written English.
+Salary:                       Negotiable
+Terms of Employment:     Yearly renewable contract.
+About You
+Qualification:           BSc Degree in Irrigation Engineering/ Water Resource Engineering or Agriculture Engineering or related field.
+ Work Experience:  Minimum of 3years experience in Irrigation activities &amp; water works.
+ Ø NGO experience is advantageous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>55797</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Menschen fuer Menschen Foundation</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Accounting / Finance, NGO Jobs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Minimum of 3 years’ or 5 years’ experience in accounting works.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Teamwork; Communication; Accounting</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>id="how-to-apply-section" class="job-detail-description"&gt;
+How To Apply
+Interested applicants fulfilling the above requirement can send a non-returnable application mentioning the job title and duty station in the subject line, CV, and copies of relevant documents to the following address or in person to the project offices stated above within 10 days from the date of announcement.
+Qualified applicants will be contacted by phone.
+Menschen fuer Menschen Foundation
+P.O.BOX  2568
+ADDIS ABABA, ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://harmeejobs.com/job/accountant-56/</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>HarmeeJobs</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:16:59 UTC</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>rss_feed</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>About the Job
+Menschen fuer Menschen Foundation- is a nongovernmental, nonreligious and nonpartisan humanitarian organization involved in Integrated Rural Development activities wishes to invite applicants with the following qualification and experience for Gofa and Boreda Integrated Rural Development Project (IRDP):
+Position:  Accountant
+Language:  A good command of spoken &amp; written English
+Salary:  Negotiable
+Terms of Employment:  Yearly renewable contract
+About You
+Qualifications:  BA/BSc or Diploma in Accounting
+ Work Experience:              Minimum of 3 years’ or 5 years’ experience in accounting works.
+NGO experience is advantageous.
+Duty Station:  Boreda IRDP, (Gamo Zone, Boreda District).
+Gofa IRDP, (Gofa Zone, Sawila town)                                      
+Main duties:
+Handling checks payments and collections.
+Preparing check payment vouchers and checks.
+Keeping the register updated and the balance as well.
+Reconciling bank statement with registers.
+Preparing monthly financial report.
+Maintain up-to-date record of accounts using accounting software.
+ Skills REQUIRED: Computer literacy and IT skills with practical experience in accounting
+software such as Peachtree Accounting…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5711,7 +6982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5820,6 +7091,19 @@
       </c>
       <c r="C8" t="n">
         <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:17:03 UTC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -6982,7 +6982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7103,6 +7103,19 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:57:25 UTC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>48</v>
       </c>
     </row>

--- a/harmeejobs_tracker.xlsx
+++ b/harmeejobs_tracker.xlsx
@@ -6982,7 +6982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7116,6 +7116,19 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:53:18 UTC</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
         <v>48</v>
       </c>
     </row>
